--- a/binding-contract/sheet-metadata.xlsx
+++ b/binding-contract/sheet-metadata.xlsx
@@ -8,11 +8,74 @@
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+  </cellXfs>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="2" width="18.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/binding-contract/sheet-metadata.xlsx
+++ b/binding-contract/sheet-metadata.xlsx
@@ -6,6 +6,35 @@
     <sheet name="Lists" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Ana</author>
+    <author>Bo</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+          </rPr>
+          <t>Ana:</t>
+        </r>
+        <r>
+          <t xml:space="preserve"> check &amp; confirm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="1">
+      <text>
+        <t>Plain note</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,7 +98,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="2" width="18.5" customWidth="1"/>
   </cols>
@@ -91,6 +120,10 @@
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" display="Docs" tooltip="Open the docs"/>
+    <hyperlink ref="B5:C5" location="Lists!A1" display="Lists"/>
+  </hyperlinks>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
